--- a/artfynd/A 43616-2025 artfynd.xlsx
+++ b/artfynd/A 43616-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102398011</v>
+        <v>102398018</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591202.0517115826</v>
+        <v>591203</v>
       </c>
       <c r="R2" t="n">
-        <v>6974196.845610388</v>
+        <v>6974197</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,19 +759,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102398018</v>
+        <v>102398011</v>
       </c>
       <c r="B3" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,26 +800,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +829,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -860,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591202.0517115826</v>
+        <v>591203</v>
       </c>
       <c r="R3" t="n">
-        <v>6974196.845610388</v>
+        <v>6974197</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -893,19 +873,9 @@
           <t>2022-07-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 43616-2025 artfynd.xlsx
+++ b/artfynd/A 43616-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,8 +910,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398011</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>